--- a/examples/reports/Tomography_Report_Bell_State_Simple.xlsx
+++ b/examples/reports/Tomography_Report_Bell_State_Simple.xlsx
@@ -541,7 +541,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Method</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>0.6961</t>
+          <t>0.6973</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -659,16 +659,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>4000</v>
+        <v>4044</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>3909</v>
+        <v>3847</v>
       </c>
     </row>
     <row r="3">
@@ -678,16 +678,16 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>1989</v>
+        <v>2054</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>2054</v>
+        <v>2072</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>2077</v>
+        <v>2002</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2072</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="4">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2048</v>
+        <v>2101</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1996</v>
+        <v>2012</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>2060</v>
+        <v>2018</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2088</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="5">
@@ -716,16 +716,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2076</v>
+        <v>2128</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>2018</v>
+        <v>2006</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1970</v>
+        <v>1954</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2128</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="6">
@@ -735,16 +735,16 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3917</v>
+        <v>3954</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3954</v>
+        <v>3915</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>145</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7">
@@ -754,16 +754,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2013</v>
+        <v>2073</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2059</v>
+        <v>2069</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2119</v>
+        <v>2044</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2001</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="8">
@@ -773,16 +773,16 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>2085</v>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>1961</v>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>2047</v>
-      </c>
       <c r="D8" s="4" t="n">
-        <v>2163</v>
+        <v>2065</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2021</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="9">
@@ -795,13 +795,13 @@
         <v>2069</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2007</v>
+        <v>2103</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2086</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="10">
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>3888</v>
+        <v>3940</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4025</v>
+        <v>4012</v>
       </c>
     </row>
   </sheetData>
@@ -878,16 +878,16 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>0.48828125</v>
+        <v>0.49365234375</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>0.01953125</v>
+        <v>0.017578125</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>0.0150146484375</v>
+        <v>0.0191650390625</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.4771728515625</v>
+        <v>0.4696044921875</v>
       </c>
     </row>
     <row r="3">
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>0.2427978515625</v>
+        <v>0.250732421875</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>0.250732421875</v>
+        <v>0.2529296875</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>0.2535400390625</v>
+        <v>0.244384765625</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.2529296875</v>
+        <v>0.251953125</v>
       </c>
     </row>
     <row r="4">
@@ -916,16 +916,16 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0.25</v>
+        <v>0.2564697265625</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.24365234375</v>
+        <v>0.24560546875</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.25146484375</v>
+        <v>0.246337890625</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.2548828125</v>
+        <v>0.2515869140625</v>
       </c>
     </row>
     <row r="5">
@@ -935,16 +935,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.25341796875</v>
+        <v>0.259765625</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.246337890625</v>
+        <v>0.244873046875</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.240478515625</v>
+        <v>0.238525390625</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.259765625</v>
+        <v>0.2568359375</v>
       </c>
     </row>
     <row r="6">
@@ -954,16 +954,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.021484375</v>
+        <v>0.01904296875</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.4781494140625</v>
+        <v>0.482666015625</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.482666015625</v>
+        <v>0.4779052734375</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.0177001953125</v>
+        <v>0.0203857421875</v>
       </c>
     </row>
     <row r="7">
@@ -973,16 +973,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>0.2457275390625</v>
+        <v>0.2530517578125</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.2513427734375</v>
+        <v>0.2525634765625</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.2586669921875</v>
+        <v>0.24951171875</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.2442626953125</v>
+        <v>0.244873046875</v>
       </c>
     </row>
     <row r="8">
@@ -992,16 +992,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
+        <v>0.2545166015625</v>
+      </c>
+      <c r="C8" s="5" t="n">
         <v>0.2393798828125</v>
       </c>
-      <c r="C8" s="5" t="n">
-        <v>0.2498779296875</v>
-      </c>
       <c r="D8" s="5" t="n">
-        <v>0.2640380859375</v>
+        <v>0.2520751953125</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.2467041015625</v>
+        <v>0.2540283203125</v>
       </c>
     </row>
     <row r="9">
@@ -1014,13 +1014,13 @@
         <v>0.2525634765625</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.2449951171875</v>
+        <v>0.2567138671875</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.247802734375</v>
+        <v>0.24658203125</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.254638671875</v>
+        <v>0.244140625</v>
       </c>
     </row>
     <row r="10">
@@ -1030,16 +1030,16 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>0.474609375</v>
+        <v>0.48095703125</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.016357421875</v>
+        <v>0.0142822265625</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.0177001953125</v>
+        <v>0.0150146484375</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.4913330078125</v>
+        <v>0.48974609375</v>
       </c>
     </row>
   </sheetData>
